--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EB0737-6151-4151-BA64-6F9338E083A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237E3179-DFF6-45EC-9CD3-8821B1F5D60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37620" yWindow="780" windowWidth="32745" windowHeight="15285" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-35745" yWindow="3360" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>locatives</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -346,150 +346,14 @@
     <t>hook_title</t>
   </si>
   <si>
-    <t>hook_image_path</t>
-  </si>
-  <si>
-    <t>situation_subtitle</t>
-  </si>
-  <si>
-    <t>cta_text</t>
-  </si>
-  <si>
     <t>syllable_times_ms</t>
   </si>
   <si>
-    <t>sound_path</t>
-  </si>
-  <si>
     <t>fruit_store</t>
   </si>
   <si>
-    <r>
-      <t>과일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>가게</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>필수</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단어</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">! </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>이것만</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>알아도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFB5CEA8"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>된다</t>
-    </r>
-  </si>
-  <si>
-    <t>사과 뜻을 외워보세요.,단어장 본편에서 더 보기 ⬇</t>
+    <t>단어를 외우자</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1175,39 +1039,24 @@
       <c r="D1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" t="s">
-        <v>19</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>20103</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G2" s="13"/>
       <c r="L2" s="12"/>
@@ -1215,6 +1064,18 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>20104</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>17</v>
+      </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
     </row>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{237E3179-DFF6-45EC-9CD3-8821B1F5D60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5FCED2-A0C2-456B-BC97-895ED66A564D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35745" yWindow="3360" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-33180" yWindow="4560" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,142 +34,35 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
-  <si>
-    <t>locatives</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>word_id</t>
+  </si>
+  <si>
+    <t>hook_title</t>
+  </si>
+  <si>
+    <t>fruit_store</t>
+  </si>
+  <si>
+    <t>단어를 외우자</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>ko_narration_id</t>
+  </si>
+  <si>
+    <t>video_path</t>
+  </si>
+  <si>
     <r>
-      <t>{我}{在}{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>저는 여기 있어요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>은행은 저기에 있어요</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>어디 가세요?</t>
-  </si>
-  <si>
-    <r>
-      <t>얼화(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>化):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 북방 지역에서는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(r)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>을 붙여 말하</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>你</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}{</t>
+      <t>resource/video/苹果多少</t>
     </r>
     <r>
       <rPr>
@@ -177,94 +70,10 @@
         <color theme="1"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
-        <charset val="129"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>去}{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>哪儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>}?</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>{</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>行}{在}{那</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>}</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/locatives/我在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这儿</t>
+      <t>钱</t>
     </r>
     <r>
       <rPr>
@@ -277,82 +86,9 @@
       </rPr>
       <t>.mp4</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/locatives/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft JhengHei"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>你去哪儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>resource/video/locatives/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>银行在那儿</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.mp4</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>topic</t>
-  </si>
-  <si>
-    <t>word_id</t>
-  </si>
-  <si>
-    <t>hook_title</t>
-  </si>
-  <si>
-    <t>syllable_times_ms</t>
-  </si>
-  <si>
-    <t>fruit_store</t>
-  </si>
-  <si>
-    <t>단어를 외우자</t>
+  </si>
+  <si>
+    <t>20103|20104</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="30">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,13 +119,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft YaHei"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -463,50 +192,21 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF57A64A"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
       <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF57A64A"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Microsoft JhengHei"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -533,34 +233,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans KR"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF4EC9B0"/>
       <name val="Consolas"/>
@@ -573,6 +245,14 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -609,67 +289,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1014,7 +694,7 @@
     <col min="2" max="2" width="4.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.75" customWidth="1"/>
+    <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="46.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.625" customWidth="1"/>
     <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
@@ -1028,35 +708,44 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="11" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2">
-        <v>20103</v>
+      <c r="C2" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
       </c>
       <c r="G2" s="13"/>
       <c r="L2" s="12"/>
@@ -1064,18 +753,7 @@
       <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3">
-        <v>20104</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>17</v>
-      </c>
+      <c r="D3" s="21"/>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
     </row>
@@ -1150,94 +828,49 @@
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="3:13">
       <c r="D17" s="5"/>
       <c r="F17" s="4"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="3:13">
       <c r="D18" s="6"/>
       <c r="E18" s="2"/>
       <c r="G18" s="4"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="3:13">
       <c r="F19" s="4"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="3:13">
       <c r="D20" s="7"/>
       <c r="E20" s="8"/>
       <c r="G20" s="4"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="3:13">
       <c r="F21" s="4"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="3:13">
       <c r="D28" s="9"/>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" spans="1:13" ht="18">
-      <c r="A29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29">
-        <v>99</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="18">
-      <c r="A30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30">
-        <v>100</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
+    <row r="29" spans="3:13">
+      <c r="G29" s="19"/>
+    </row>
+    <row r="30" spans="3:13">
+      <c r="C30" s="7"/>
       <c r="F30" s="18"/>
     </row>
-    <row r="31" spans="1:13">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31">
-        <v>101</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" t="s">
-        <v>9</v>
-      </c>
+    <row r="31" spans="3:13">
+      <c r="C31" s="7"/>
       <c r="G31" s="4"/>
     </row>
   </sheetData>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5FCED2-A0C2-456B-BC97-895ED66A564D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1E551-AFCF-4846-B50D-2AD440C08048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33180" yWindow="4560" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-35685" yWindow="3765" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -48,32 +48,28 @@
     <t>hook_title</t>
   </si>
   <si>
-    <t>fruit_store</t>
-  </si>
-  <si>
-    <t>단어를 외우자</t>
+    <t>ko_narration_id</t>
+  </si>
+  <si>
+    <t>video_path</t>
+  </si>
+  <si>
+    <t>bao</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ko_narration_id</t>
-  </si>
-  <si>
-    <t>video_path</t>
-  </si>
-  <si>
     <r>
-      <t>resource/video/苹果多少</t>
+      <t>resource/video/</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
       </rPr>
-      <t>钱</t>
+      <t>宝家</t>
     </r>
     <r>
       <rPr>
@@ -86,9 +82,20 @@
       </rPr>
       <t>.mp4</t>
     </r>
-  </si>
-  <si>
-    <t>20103|20104</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sound_repeat_count</t>
+  </si>
+  <si>
+    <t>after_sound_delay_sec</t>
+  </si>
+  <si>
+    <t>에버랜드 푸바오는\n왜 돌림자 '바오'를 사용할까?</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30123|30124|30125|30126|30127|30128</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -249,10 +256,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -693,9 +699,9 @@
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="46.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.625" customWidth="1"/>
     <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
@@ -720,34 +726,45 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>9</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" ht="18.75">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>2</v>
-      </c>
-      <c r="G2" s="13"/>
+        <v>1000</v>
+      </c>
+      <c r="G2" s="13">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1.2</v>
+      </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="O2" s="4"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D1E551-AFCF-4846-B50D-2AD440C08048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF88BF3-0DE7-4798-8491-F88383189F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35685" yWindow="3765" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -702,8 +702,8 @@
     <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.625" customWidth="1"/>
-    <col min="8" max="8" width="35.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF88BF3-0DE7-4798-8491-F88383189F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97B67F1-3999-4AB7-9A42-FAAD1F097267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97B67F1-3999-4AB7-9A42-FAAD1F097267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E067734-C40B-4FC5-9EDA-F14E67CC7261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -98,12 +98,66 @@
     <t>30123|30124|30125|30126|30127|30128</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>zhuxi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 정치인</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30129|30130|30131|30132|30133</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>jingyesi</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50000|50001|50002|50003</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국 초등학생들도 모두 아는\n전설의 한시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>jingyesi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>read_meaning_ko</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -259,6 +313,13 @@
       <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -698,13 +759,13 @@
   <cols>
     <col min="1" max="1" width="13.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="87" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.625" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
@@ -737,6 +798,9 @@
       <c r="H1" t="s">
         <v>9</v>
       </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -765,18 +829,72 @@
       <c r="H2">
         <v>1.2</v>
       </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
       <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="O2" s="4"/>
     </row>
-    <row r="3" spans="1:15">
-      <c r="D3" s="21"/>
+    <row r="3" spans="1:15" ht="18.75">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3" s="13">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
       <c r="M3" s="12"/>
       <c r="N3" s="12"/>
     </row>
     <row r="4" spans="1:15">
-      <c r="D4" s="8"/>
-      <c r="G4" s="14"/>
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="14">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="4"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E067734-C40B-4FC5-9EDA-F14E67CC7261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0323E05D-B2A4-4441-B18B-2544975A22CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="15870" yWindow="6135" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
   <si>
     <t>id</t>
   </si>
@@ -152,12 +152,22 @@
   <si>
     <t>read_meaning_ko</t>
   </si>
+  <si>
+    <t>last_hold_text</t>
+  </si>
+  <si>
+    <t>당나라 시인 이백(李白)\n &lt;정야사(靜夜思) - 고요한 밤의 그리움&gt;</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>last_hold_sec</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -320,6 +330,19 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFE394DC"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -352,7 +375,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -417,6 +440,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -766,8 +793,8 @@
     <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.625" customWidth="1"/>
+    <col min="10" max="10" width="62.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
     <col min="14" max="14" width="41" bestFit="1" customWidth="1"/>
@@ -801,6 +828,12 @@
       <c r="I1" t="s">
         <v>19</v>
       </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>22</v>
+      </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
     </row>
@@ -894,6 +927,12 @@
       </c>
       <c r="I4" t="b">
         <v>0</v>
+      </c>
+      <c r="J4" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4">
+        <v>2.8</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0323E05D-B2A4-4441-B18B-2544975A22CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359A654B-5771-4ECC-B845-0C1EA506145D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15870" yWindow="6135" windowWidth="32745" windowHeight="12480" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-32595" yWindow="2925" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -85,9 +85,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>sound_repeat_count</t>
-  </si>
-  <si>
     <t>after_sound_delay_sec</t>
   </si>
   <si>
@@ -160,14 +157,39 @@
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
   <si>
-    <t>last_hold_sec</t>
+    <t>bg_path</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>resource/sound/bg_user/Moonlight_Over_The_Stone_Path.mp3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>lee</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>50005|50006|50007|50008</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국인들도 존경하는\n한국의 장군이 쓴 한시</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이순신 장군</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>sound_repeat_count</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,12 +359,6 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFE394DC"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -375,7 +391,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -443,9 +459,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" builtinId="28"/>
@@ -789,12 +802,11 @@
     <col min="3" max="3" width="36.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="59.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="62.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="62.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
     <col min="14" max="14" width="41" bestFit="1" customWidth="1"/>
@@ -816,23 +828,23 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" t="s">
         <v>19</v>
-      </c>
-      <c r="J1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="23" t="s">
-        <v>22</v>
       </c>
       <c r="M1" s="3"/>
       <c r="O1" s="3"/>
@@ -845,24 +857,24 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1000</v>
       </c>
-      <c r="G2" s="13">
+      <c r="H2" s="13">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>1.2</v>
       </c>
-      <c r="I2" t="b">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="L2" s="12"/>
@@ -871,30 +883,30 @@
     </row>
     <row r="3" spans="1:15" ht="18.75">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1000</v>
       </c>
-      <c r="G3" s="13">
+      <c r="H3" s="13">
         <v>1</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>1.2</v>
       </c>
-      <c r="I3" t="b">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="M3" s="12"/>
@@ -902,43 +914,76 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>3</v>
       </c>
       <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4">
         <v>1001</v>
       </c>
-      <c r="G4" s="14">
+      <c r="H4" s="14">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="I4" t="b">
+      <c r="J4" t="b">
         <v>0</v>
       </c>
-      <c r="J4" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="K4">
-        <v>2.8</v>
+      <c r="K4" s="22" t="s">
+        <v>20</v>
       </c>
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="4"/>
     </row>
     <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5">
+        <v>1002</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359A654B-5771-4ECC-B845-0C1EA506145D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034C58A-4171-497F-85AA-C7F0F344BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32595" yWindow="2925" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -182,6 +182,36 @@
   </si>
   <si>
     <t>sound_repeat_count</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>use_word_video_audio</t>
+  </si>
+  <si>
+    <r>
+      <t>resource/video/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>lee</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.mp4</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -802,8 +832,8 @@
     <col min="3" max="3" width="36.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="52.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="59.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.25" customWidth="1"/>
     <col min="8" max="9" width="21.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="62.75" bestFit="1" customWidth="1"/>
@@ -828,22 +858,25 @@
       <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>19</v>
       </c>
       <c r="M1" s="3"/>
@@ -865,19 +898,21 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2">
         <v>1000</v>
       </c>
-      <c r="H2" s="13">
+      <c r="I2" s="13">
         <v>1</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>1.2</v>
       </c>
-      <c r="J2" t="b">
+      <c r="K2" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="12"/>
       <c r="M2" s="12"/>
       <c r="O2" s="4"/>
     </row>
@@ -897,16 +932,19 @@
       <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="G3">
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3">
         <v>1000</v>
       </c>
-      <c r="H3" s="13">
+      <c r="I3" s="13">
         <v>1</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>1.2</v>
       </c>
-      <c r="J3" t="b">
+      <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="M3" s="12"/>
@@ -928,22 +966,25 @@
       <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>22</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1001</v>
       </c>
-      <c r="H4" s="14">
+      <c r="I4" s="14">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0</v>
       </c>
-      <c r="J4" t="b">
+      <c r="K4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="L4" s="22" t="s">
         <v>20</v>
       </c>
       <c r="M4" s="12"/>
@@ -964,27 +1005,29 @@
         <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1002</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0</v>
       </c>
-      <c r="J5" t="b">
+      <c r="K5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="12"/>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>
     </row>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2034C58A-4171-497F-85AA-C7F0F344BAA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84BFA43-BD79-4D14-8201-616242BDFB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
@@ -33,6 +33,198 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Chan Park</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{22A5667E-0C0B-4B36-AE21-1BB0DCF02459}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Chan Park:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>비디오의</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>오디오를</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>재생할지</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">말지
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{C3D29341-A800-4CED-83FD-FBC9DC50F4FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Chan Park:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>한국어</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>뜻을</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>읽을지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t xml:space="preserve">말지
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
@@ -173,14 +365,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>중국인들도 존경하는\n한국의 장군이 쓴 한시</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이순신 장군</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>sound_repeat_count</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -214,12 +398,20 @@
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>중국인들도 존경하는\n한국의 명장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>충무공 이순신 &lt;한산도가&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,6 +581,34 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -823,7 +1043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC832AC-62FD-4F32-83D9-192679032F25}">
   <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -834,9 +1054,8 @@
     <col min="5" max="5" width="39.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="57.25" customWidth="1"/>
-    <col min="8" max="9" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="62.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
     <col min="13" max="13" width="41.625" customWidth="1"/>
     <col min="14" max="14" width="41" bestFit="1" customWidth="1"/>
@@ -859,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>21</v>
@@ -868,7 +1087,7 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
@@ -1002,10 +1221,10 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -1026,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>
@@ -1139,5 +1358,6 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A84BFA43-BD79-4D14-8201-616242BDFB23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86611CA-E1F1-4CC3-AAE0-7F402D0A6B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-32445" yWindow="2910" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -399,11 +399,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>중국인들도 존경하는\n한국의 명장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>충무공 이순신 &lt;한산도가&gt;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중국인들도 존경하는\n전설의 한국 명장</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1221,7 +1221,7 @@
         <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M5" s="12"/>
       <c r="O5" s="4"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\work\LVPD_Studio\resource\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86611CA-E1F1-4CC3-AAE0-7F402D0A6B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4625EFC-F1F5-4508-82A9-686727B0033F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32445" yWindow="2910" windowWidth="32745" windowHeight="17535" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{4ABACD07-DE77-46EA-95A9-D7C0914B6AEB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/resource/table/shorts_vocabulary_clips.xlsx
+++ b/resource/table/shorts_vocabulary_clips.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,15 +469,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>skip_word_video_tail</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>last_hold_text</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>last_hold_sec</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>bg_path</t>
         </is>
@@ -537,6 +542,7 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -592,6 +598,7 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,13 +651,14 @@
           <t>True</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>당나라 시인 이백(李白)\n &lt;정야사(靜夜思) - 고요한 밤의 그리움&gt;</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>resource/sound/bg_user/Moonlight_Over_The_Stone_Path.mp3</t>
         </is>
@@ -695,7 +703,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0|0|0|0|0</t>
+          <t>0.3|0.3|0.3|0.3|0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -710,15 +718,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>중국산 채널주인도 존경하고 있습니다!</t>
+          <t>true</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>중국산인 채널주인도 존경함!</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>resource/sound/bg_short/동양풍1.mp3</t>
         </is>
